--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.75607</v>
+        <v>16.40854</v>
       </c>
       <c r="D2" t="n">
-        <v>16.67662</v>
+        <v>16.27151</v>
       </c>
       <c r="E2" t="n">
-        <v>16.64208</v>
+        <v>16.30729</v>
       </c>
       <c r="F2" t="n">
-        <v>42.52997</v>
+        <v>42.74902</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05032</v>
+        <v>0.05101</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80385</v>
+        <v>1.78225</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.57649</v>
+        <v>16.7602</v>
       </c>
       <c r="D3" t="n">
-        <v>16.41956</v>
+        <v>16.43572</v>
       </c>
       <c r="E3" t="n">
-        <v>16.28194</v>
+        <v>16.52782</v>
       </c>
       <c r="F3" t="n">
-        <v>42.60566</v>
+        <v>41.88768</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05117</v>
+        <v>0.05058</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81455</v>
+        <v>1.83684</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.81871</v>
+        <v>16.70574</v>
       </c>
       <c r="D4" t="n">
-        <v>16.55075</v>
+        <v>16.58424</v>
       </c>
       <c r="E4" t="n">
-        <v>17.06884</v>
+        <v>16.59978</v>
       </c>
       <c r="F4" t="n">
-        <v>42.39369</v>
+        <v>42.06916</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05053</v>
+        <v>0.05191</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82137</v>
+        <v>1.81322</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.69715</v>
+        <v>17.1401</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10594</v>
+        <v>15.6386</v>
       </c>
       <c r="E6" t="n">
-        <v>16.3547</v>
+        <v>16.30656</v>
       </c>
       <c r="F6" t="n">
-        <v>21.69447</v>
+        <v>21.81405</v>
       </c>
       <c r="G6" t="n">
-        <v>34.1323</v>
+        <v>34.30329</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.75554</v>
+        <v>16.78493</v>
       </c>
       <c r="D7" t="n">
-        <v>16.00564</v>
+        <v>16.0434</v>
       </c>
       <c r="E7" t="n">
-        <v>16.42089</v>
+        <v>16.28162</v>
       </c>
       <c r="F7" t="n">
-        <v>22.22825</v>
+        <v>21.49154</v>
       </c>
       <c r="G7" t="n">
-        <v>34.09171</v>
+        <v>34.24413</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.95681</v>
+        <v>16.51485</v>
       </c>
       <c r="D8" t="n">
-        <v>16.05967</v>
+        <v>16.16294</v>
       </c>
       <c r="E8" t="n">
-        <v>16.32444</v>
+        <v>16.22151</v>
       </c>
       <c r="F8" t="n">
-        <v>21.66385</v>
+        <v>21.54651</v>
       </c>
       <c r="G8" t="n">
-        <v>34.64347</v>
+        <v>33.78386</v>
       </c>
     </row>
   </sheetData>
